--- a/data/trans_orig/P1404-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P1404-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de colesterol alto en 2007</t>
+          <t>Población con diagnóstico de colesterol alto en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>125532</t>
+          <t>124557</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>167802</t>
+          <t>168455</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>211495</t>
+          <t>214017</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>271752</t>
+          <t>272422</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>350858</t>
+          <t>351681</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>423648</t>
+          <t>419643</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>17,88%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>863921</t>
+          <t>863268</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>906191</t>
+          <t>907166</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>83,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>87,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1043361</t>
+          <t>1042691</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1103618</t>
+          <t>1101096</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,34%</t>
+          <t>79,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,92%</t>
+          <t>83,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1923187</t>
+          <t>1927192</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1995977</t>
+          <t>1995154</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,95%</t>
+          <t>82,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,05%</t>
+          <t>85,01%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>69829</t>
+          <t>72426</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>108800</t>
+          <t>108599</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>69432</t>
+          <t>71171</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>107608</t>
+          <t>108966</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>150994</t>
+          <t>152538</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>203043</t>
+          <t>205948</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,28%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1584613</t>
+          <t>1584814</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1623584</t>
+          <t>1620987</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1480065</t>
+          <t>1478707</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1518241</t>
+          <t>1516502</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3078043</t>
+          <t>3075138</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3130092</t>
+          <t>3128548</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,35%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17821</t>
+          <t>17107</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>36843</t>
+          <t>38317</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12776</t>
+          <t>12440</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30155</t>
+          <t>31100</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>34046</t>
+          <t>34292</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>61546</t>
+          <t>62307</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,06%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>514565</t>
+          <t>513091</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>533587</t>
+          <t>534301</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>446257</t>
+          <t>445312</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>463636</t>
+          <t>463972</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>966274</t>
+          <t>965513</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>993774</t>
+          <t>993528</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,66%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>231228</t>
+          <t>229997</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>294029</t>
+          <t>291763</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>314712</t>
+          <t>312640</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>383461</t>
+          <t>385338</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>561745</t>
+          <t>561635</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>655564</t>
+          <t>658087</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,89%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2982514</t>
+          <t>2984780</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3045315</t>
+          <t>3046546</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,03%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2995736</t>
+          <t>2993859</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3064485</t>
+          <t>3066557</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6000177</t>
+          <t>5997654</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6093996</t>
+          <t>6094106</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de colesterol alto en 2012</t>
+          <t>Población con diagnóstico de colesterol alto en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>191548</t>
+          <t>192801</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>245147</t>
+          <t>247690</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>322999</t>
+          <t>321399</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>391940</t>
+          <t>386891</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>532302</t>
+          <t>531215</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>620449</t>
+          <t>615440</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>26,61%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>729496</t>
+          <t>726953</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>783095</t>
+          <t>781842</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>74,85%</t>
+          <t>74,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,35%</t>
+          <t>80,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>945857</t>
+          <t>950906</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1014798</t>
+          <t>1016398</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>70,7%</t>
+          <t>71,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>75,86%</t>
+          <t>75,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1691991</t>
+          <t>1697000</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1780138</t>
+          <t>1781225</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>73,17%</t>
+          <t>73,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,98%</t>
+          <t>77,03%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>112601</t>
+          <t>112912</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>162657</t>
+          <t>161543</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>98559</t>
+          <t>96423</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>142888</t>
+          <t>142254</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>224963</t>
+          <t>225329</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>289382</t>
+          <t>291535</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,84%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1799892</t>
+          <t>1801006</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1849948</t>
+          <t>1849637</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>91,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1611704</t>
+          <t>1612338</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1656033</t>
+          <t>1658169</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>91,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3427759</t>
+          <t>3425606</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3492178</t>
+          <t>3491812</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>93,94%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>25580</t>
+          <t>24104</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>52666</t>
+          <t>50926</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10341</t>
+          <t>10895</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>29363</t>
+          <t>29302</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>38774</t>
+          <t>39658</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>70742</t>
+          <t>72604</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,73%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>428515</t>
+          <t>430255</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>455601</t>
+          <t>457077</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>429268</t>
+          <t>429329</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>448290</t>
+          <t>447736</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>869071</t>
+          <t>867209</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>901039</t>
+          <t>900155</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,78%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>347774</t>
+          <t>349739</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>424871</t>
+          <t>428285</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>450749</t>
+          <t>450398</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>533878</t>
+          <t>538087</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>825025</t>
+          <t>815847</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>934945</t>
+          <t>936248</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,43%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2993502</t>
+          <t>2990088</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3070599</t>
+          <t>3068634</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>87,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3017142</t>
+          <t>3012933</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3100271</t>
+          <t>3100622</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,97%</t>
+          <t>84,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,31%</t>
+          <t>87,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6034448</t>
+          <t>6033145</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6144368</t>
+          <t>6153546</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,58%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>88,29%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de colesterol alto en 2016</t>
+          <t>Población con diagnóstico de colesterol alto en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>156591</t>
+          <t>158066</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>200881</t>
+          <t>202025</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>240586</t>
+          <t>242213</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>301513</t>
+          <t>301329</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>30,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>414024</t>
+          <t>416870</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>487495</t>
+          <t>488999</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>27,96%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>553466</t>
+          <t>552322</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>597756</t>
+          <t>596281</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,37%</t>
+          <t>73,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>79,24%</t>
+          <t>79,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>693147</t>
+          <t>693331</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>754074</t>
+          <t>752447</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>69,69%</t>
+          <t>69,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>75,81%</t>
+          <t>75,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1261512</t>
+          <t>1260008</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1334983</t>
+          <t>1332137</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>72,13%</t>
+          <t>72,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,33%</t>
+          <t>76,17%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>140439</t>
+          <t>140325</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>188155</t>
+          <t>187954</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4302,7 +4302,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>136607</t>
+          <t>140694</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>187753</t>
+          <t>191650</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>288283</t>
+          <t>290016</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>358137</t>
+          <t>361954</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,9%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1888230</t>
+          <t>1888431</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1935946</t>
+          <t>1936060</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,7 +4410,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>90,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1800547</t>
+          <t>1796650</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1851693</t>
+          <t>1847606</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>90,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>92,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3706548</t>
+          <t>3702731</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3776402</t>
+          <t>3774669</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,86%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>33001</t>
+          <t>33542</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>62893</t>
+          <t>62864</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>23235</t>
+          <t>23368</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>49825</t>
+          <t>47885</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>62054</t>
+          <t>64629</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>98973</t>
+          <t>102512</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,35%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>483993</t>
+          <t>484022</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>513885</t>
+          <t>513344</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,5%</t>
+          <t>88,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>499315</t>
+          <t>501255</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>525905</t>
+          <t>525772</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>91,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>997054</t>
+          <t>993515</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1033973</t>
+          <t>1031398</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>90,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,1%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>351483</t>
+          <t>350813</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>429372</t>
+          <t>425940</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>431429</t>
+          <t>427143</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>515578</t>
+          <t>515984</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>801723</t>
+          <t>799331</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>912461</t>
+          <t>911933</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,2%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2948246</t>
+          <t>2951678</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3026135</t>
+          <t>3026805</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>87,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>89,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3016522</t>
+          <t>3016116</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3100671</t>
+          <t>3104957</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>85,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,79%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5997257</t>
+          <t>5997785</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6107995</t>
+          <t>6110387</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,79%</t>
+          <t>86,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,4%</t>
+          <t>88,43%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de colesterol alto en 2023</t>
+          <t>Población con diagnóstico de colesterol alto en 2023 (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>119642</t>
+          <t>119763</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>154928</t>
+          <t>154241</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,47 +5557,47 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
+          <t>30,23%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>493</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>245059</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>227823</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>266656</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>32,66%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
           <t>30,36%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>493</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>245059</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>226067</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>265994</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>32,66%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>30,13%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>353979</t>
+          <t>354587</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>410441</t>
+          <t>408683</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>32,42%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>355318</t>
+          <t>356005</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>390604</t>
+          <t>390483</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,49 +5670,49 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
+          <t>69,77%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>76,53%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>928</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>505298</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>483701</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>522534</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>67,34%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>64,46%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
           <t>69,64%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>76,55%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>928</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>505298</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>484363</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>524290</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>67,34%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>64,55%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>69,87%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>1410</t>
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>850162</t>
+          <t>851920</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>906624</t>
+          <t>906016</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>67,44%</t>
+          <t>67,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,92%</t>
+          <t>71,87%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>175472</t>
+          <t>183639</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>300828</t>
+          <t>298442</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>241474</t>
+          <t>241774</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>882852</t>
+          <t>919345</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>41,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>481473</t>
+          <t>480029</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1277600</t>
+          <t>1281332</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>28,34%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1986155</t>
+          <t>1988541</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2111511</t>
+          <t>2103344</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,85%</t>
+          <t>86,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1351522</t>
+          <t>1315029</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1992900</t>
+          <t>1992600</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>60,49%</t>
+          <t>58,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3243757</t>
+          <t>3240025</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4039884</t>
+          <t>4041328</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>71,74%</t>
+          <t>71,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
+          <t>89,38%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>60382</t>
+          <t>59857</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>91269</t>
+          <t>90909</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>65954</t>
+          <t>65867</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>91874</t>
+          <t>92531</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>133291</t>
+          <t>133941</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>174406</t>
+          <t>174627</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,36%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>555354</t>
+          <t>555714</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>586241</t>
+          <t>586766</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,89%</t>
+          <t>85,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>568269</t>
+          <t>567612</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>594189</t>
+          <t>594276</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,08%</t>
+          <t>85,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>90,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1132360</t>
+          <t>1132139</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1173475</t>
+          <t>1172825</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,65%</t>
+          <t>86,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>89,75%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>363917</t>
+          <t>366353</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>515200</t>
+          <t>520141</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>574433</t>
+          <t>566969</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1365630</t>
+          <t>1392990</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,47%</t>
+          <t>38,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1009845</t>
+          <t>1012891</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1884086</t>
+          <t>1900234</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,81%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2928652</t>
+          <t>2923711</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3079935</t>
+          <t>3077499</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,04%</t>
+          <t>84,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,43%</t>
+          <t>89,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2279244</t>
+          <t>2251884</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3070441</t>
+          <t>3077905</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,53%</t>
+          <t>61,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>84,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5204640</t>
+          <t>5188492</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6078881</t>
+          <t>6075835</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,42%</t>
+          <t>73,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,75%</t>
+          <t>85,71%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1404-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P1404-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>124557</t>
+          <t>126448</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>168455</t>
+          <t>170939</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,47 +748,47 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
+          <t>16,57%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>239785</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>214808</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>268101</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>18,23%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
           <t>16,33%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>233</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>239785</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>214017</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>272422</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>18,23%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>16,27%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>351681</t>
+          <t>349800</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>419643</t>
+          <t>423644</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>18,05%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>863268</t>
+          <t>860784</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>907166</t>
+          <t>905275</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,49 +861,49 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
+          <t>83,43%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>87,74%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1058</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>1075328</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>1047012</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>1100305</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>81,77%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>79,61%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
           <t>83,67%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>87,93%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>1058</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>1075328</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>1042691</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>1101096</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>81,77%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>79,29%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>83,73%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>1942</t>
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1927192</t>
+          <t>1923191</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1995154</t>
+          <t>1997035</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>81,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,01%</t>
+          <t>85,09%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>72426</t>
+          <t>72292</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>108599</t>
+          <t>106999</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>71171</t>
+          <t>71005</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>108966</t>
+          <t>110350</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>205948</t>
+          <t>206404</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,29%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1584814</t>
+          <t>1586414</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1620987</t>
+          <t>1621121</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1478707</t>
+          <t>1477323</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1516502</t>
+          <t>1516668</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3075138</t>
+          <t>3074682</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17107</t>
+          <t>16856</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38317</t>
+          <t>36082</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12440</t>
+          <t>13122</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>31100</t>
+          <t>30431</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>34292</t>
+          <t>34343</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>62307</t>
+          <t>60910</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>5,93%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>513091</t>
+          <t>515326</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>534301</t>
+          <t>534552</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>445312</t>
+          <t>445981</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>463972</t>
+          <t>463290</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>965513</t>
+          <t>966910</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>993528</t>
+          <t>993477</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>229997</t>
+          <t>227814</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>291763</t>
+          <t>290827</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>312640</t>
+          <t>312230</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>385338</t>
+          <t>383320</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>561635</t>
+          <t>562402</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>658087</t>
+          <t>654366</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,83%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2984780</t>
+          <t>2985716</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3046546</t>
+          <t>3048729</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>91,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2993859</t>
+          <t>2995877</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3066557</t>
+          <t>3066967</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>88,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5997654</t>
+          <t>6001375</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6094106</t>
+          <t>6093339</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>91,55%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>192801</t>
+          <t>191008</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>247690</t>
+          <t>242639</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>321399</t>
+          <t>321810</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>386891</t>
+          <t>387672</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>531215</t>
+          <t>533696</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>615440</t>
+          <t>618349</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>26,74%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>726953</t>
+          <t>732004</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>781842</t>
+          <t>783635</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>74,59%</t>
+          <t>75,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,22%</t>
+          <t>80,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>950906</t>
+          <t>950125</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1016398</t>
+          <t>1015987</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>71,08%</t>
+          <t>71,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>75,98%</t>
+          <t>75,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1697000</t>
+          <t>1694091</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1781225</t>
+          <t>1778744</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>73,39%</t>
+          <t>73,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>77,03%</t>
+          <t>76,92%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>112912</t>
+          <t>112861</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>161543</t>
+          <t>159864</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2699,7 +2699,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>96423</t>
+          <t>95978</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>142254</t>
+          <t>142021</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>225329</t>
+          <t>223051</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>291535</t>
+          <t>289872</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,8%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1801006</t>
+          <t>1802685</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1849637</t>
+          <t>1849688</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1612338</t>
+          <t>1612571</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1658169</t>
+          <t>1658614</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3425606</t>
+          <t>3427269</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3491812</t>
+          <t>3494090</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>94,0%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>24104</t>
+          <t>24529</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>50926</t>
+          <t>51915</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10895</t>
+          <t>9592</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>29302</t>
+          <t>28111</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>39658</t>
+          <t>40008</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>72604</t>
+          <t>72005</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,66%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>430255</t>
+          <t>429266</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>457077</t>
+          <t>456652</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>429329</t>
+          <t>430520</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>447736</t>
+          <t>449039</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>867209</t>
+          <t>867808</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>900155</t>
+          <t>899805</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,74%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>349739</t>
+          <t>349907</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>428285</t>
+          <t>427182</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>450398</t>
+          <t>452390</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>538087</t>
+          <t>535114</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>815847</t>
+          <t>824488</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>936248</t>
+          <t>937665</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,45%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2990088</t>
+          <t>2991191</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3068634</t>
+          <t>3068466</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,47%</t>
+          <t>87,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,77%</t>
+          <t>89,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3012933</t>
+          <t>3015906</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3100622</t>
+          <t>3098630</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,85%</t>
+          <t>84,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,32%</t>
+          <t>87,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6033145</t>
+          <t>6031728</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6153546</t>
+          <t>6144905</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,57%</t>
+          <t>86,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,29%</t>
+          <t>88,17%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>158066</t>
+          <t>156723</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>202025</t>
+          <t>203074</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>242213</t>
+          <t>243704</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>301329</t>
+          <t>299605</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>416870</t>
+          <t>413583</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>488999</t>
+          <t>489020</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,7 +4024,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>552322</t>
+          <t>551273</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>596281</t>
+          <t>597624</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,22%</t>
+          <t>73,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>79,05%</t>
+          <t>79,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>693331</t>
+          <t>695055</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>752447</t>
+          <t>750956</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>69,71%</t>
+          <t>69,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>75,65%</t>
+          <t>75,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1260008</t>
+          <t>1259987</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1332137</t>
+          <t>1335424</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4142,7 +4142,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,17%</t>
+          <t>76,35%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>140325</t>
+          <t>137904</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>187954</t>
+          <t>186192</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>140694</t>
+          <t>137747</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>191650</t>
+          <t>190140</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>290016</t>
+          <t>292054</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>361954</t>
+          <t>359149</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,84%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1888431</t>
+          <t>1890193</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1936060</t>
+          <t>1938481</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>91,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1796650</t>
+          <t>1798160</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1847606</t>
+          <t>1850553</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>90,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3702731</t>
+          <t>3705536</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3774669</t>
+          <t>3772631</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>92,81%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>33542</t>
+          <t>32259</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>62864</t>
+          <t>61039</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>23368</t>
+          <t>23167</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>47885</t>
+          <t>49197</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>64629</t>
+          <t>62626</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>102512</t>
+          <t>101322</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,24%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>484022</t>
+          <t>485847</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>513344</t>
+          <t>514627</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,51%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>501255</t>
+          <t>499943</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>525772</t>
+          <t>525973</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>91,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>993515</t>
+          <t>994705</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1031398</t>
+          <t>1033401</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,29%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>350813</t>
+          <t>354641</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>425940</t>
+          <t>428951</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>427143</t>
+          <t>426977</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>515984</t>
+          <t>516507</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5023,7 +5023,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>799331</t>
+          <t>800292</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>911933</t>
+          <t>913332</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,22%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2951678</t>
+          <t>2948667</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3026805</t>
+          <t>3022977</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>87,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>89,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3016116</t>
+          <t>3015593</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3104957</t>
+          <t>3105123</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>85,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5997785</t>
+          <t>5996386</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6110387</t>
+          <t>6109426</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>86,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,43%</t>
+          <t>88,42%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>135618</t>
+          <t>143656</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>119763</t>
+          <t>125831</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>154241</t>
+          <t>161580</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>245059</t>
+          <t>262215</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>227823</t>
+          <t>241615</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>266656</t>
+          <t>281519</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>29,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>34,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>380677</t>
+          <t>405871</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>354587</t>
+          <t>380285</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>408683</t>
+          <t>434934</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>31,25%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>374628</t>
+          <t>429988</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>356005</t>
+          <t>412064</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>390483</t>
+          <t>447813</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>73,42%</t>
+          <t>74,96%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>69,77%</t>
+          <t>71,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,53%</t>
+          <t>78,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>505298</t>
+          <t>556006</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>483701</t>
+          <t>536702</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>522534</t>
+          <t>576606</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>67,34%</t>
+          <t>67,95%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>64,46%</t>
+          <t>65,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>69,64%</t>
+          <t>70,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>879926</t>
+          <t>985994</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>851920</t>
+          <t>956931</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>906016</t>
+          <t>1011580</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>69,8%</t>
+          <t>70,84%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>67,58%</t>
+          <t>68,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,87%</t>
+          <t>72,68%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>510246</t>
+          <t>573644</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>510246</t>
+          <t>573644</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>510246</t>
+          <t>573644</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>750357</t>
+          <t>818221</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>750357</t>
+          <t>818221</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>750357</t>
+          <t>818221</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1260603</t>
+          <t>1391865</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1260603</t>
+          <t>1391865</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1260603</t>
+          <t>1391865</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>254021</t>
+          <t>278763</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>183639</t>
+          <t>250419</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>298442</t>
+          <t>314371</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>432853</t>
+          <t>247951</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>241774</t>
+          <t>226179</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>919345</t>
+          <t>271900</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,15%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>686875</t>
+          <t>526715</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>480029</t>
+          <t>486853</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1281332</t>
+          <t>563966</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>12,83%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2032962</t>
+          <t>1947984</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1988541</t>
+          <t>1912376</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2103344</t>
+          <t>1976328</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>87,48%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,95%</t>
+          <t>85,88%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>88,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1801521</t>
+          <t>1919872</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1315029</t>
+          <t>1895923</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1992600</t>
+          <t>1941644</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>80,63%</t>
+          <t>88,56%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,85%</t>
+          <t>87,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,18%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>3834482</t>
+          <t>3867855</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3240025</t>
+          <t>3830604</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4041328</t>
+          <t>3907717</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>84,81%</t>
+          <t>88,01%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>87,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>88,92%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2286983</t>
+          <t>2226747</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2286983</t>
+          <t>2226747</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2286983</t>
+          <t>2226747</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2234374</t>
+          <t>2167823</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2234374</t>
+          <t>2167823</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2234374</t>
+          <t>2167823</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4521357</t>
+          <t>4394570</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4521357</t>
+          <t>4394570</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4521357</t>
+          <t>4394570</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>74392</t>
+          <t>83519</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>59857</t>
+          <t>68035</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>90909</t>
+          <t>101678</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>78240</t>
+          <t>88764</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>65867</t>
+          <t>75649</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>92531</t>
+          <t>105570</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>152631</t>
+          <t>172283</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>133941</t>
+          <t>151497</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>174627</t>
+          <t>198274</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,72%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>572231</t>
+          <t>628068</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>555714</t>
+          <t>609909</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>586766</t>
+          <t>643552</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>88,5%</t>
+          <t>88,26%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>85,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>90,44%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>581903</t>
+          <t>644722</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>567612</t>
+          <t>627916</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>594276</t>
+          <t>657837</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>87,9%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,98%</t>
+          <t>85,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,02%</t>
+          <t>89,69%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1154135</t>
+          <t>1272790</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1132139</t>
+          <t>1246799</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1172825</t>
+          <t>1293576</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>88,32%</t>
+          <t>88,08%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,64%</t>
+          <t>86,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>89,52%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>660143</t>
+          <t>733486</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>660143</t>
+          <t>733486</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>660143</t>
+          <t>733486</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1306766</t>
+          <t>1445073</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1306766</t>
+          <t>1445073</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1306766</t>
+          <t>1445073</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>464031</t>
+          <t>505938</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>366353</t>
+          <t>464903</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>520141</t>
+          <t>543523</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>756152</t>
+          <t>598930</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>566969</t>
+          <t>568271</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1392990</t>
+          <t>638216</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>38,22%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1220182</t>
+          <t>1104869</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1012891</t>
+          <t>1058061</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1900234</t>
+          <t>1160278</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>16,04%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2979821</t>
+          <t>3006040</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2923711</t>
+          <t>2968455</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3077499</t>
+          <t>3047075</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>86,53%</t>
+          <t>85,59%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,9%</t>
+          <t>84,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,36%</t>
+          <t>86,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2888722</t>
+          <t>3120600</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2251884</t>
+          <t>3081314</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3077905</t>
+          <t>3151259</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>79,25%</t>
+          <t>83,9%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,78%</t>
+          <t>82,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>84,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>5868544</t>
+          <t>6126639</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5188492</t>
+          <t>6071230</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6075835</t>
+          <t>6173447</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>82,79%</t>
+          <t>84,72%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,19%</t>
+          <t>83,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,71%</t>
+          <t>85,37%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3443852</t>
+          <t>3511978</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3443852</t>
+          <t>3511978</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3443852</t>
+          <t>3511978</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3644874</t>
+          <t>3719530</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3644874</t>
+          <t>3719530</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3644874</t>
+          <t>3719530</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7088726</t>
+          <t>7231508</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7088726</t>
+          <t>7231508</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7088726</t>
+          <t>7231508</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
